--- a/data/trans_orig/IP1009-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Provincia-trans_orig.xlsx
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2179,7 +2179,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3783</t>
+          <t>3480</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41127</t>
+          <t>41651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82912</t>
+          <t>83215</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4066</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>132263</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>260286</t>
+          <t>261040</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3153,7 +3153,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3477</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>446</t>
+          <t>447</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>153849</t>
+          <t>153609</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>160576</t>
+          <t>160581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>316537</t>
+          <t>316732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>321516</t>
+          <t>321515</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>4250</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>677</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7090</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>677318</t>
+          <t>676771</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717142</t>
+          <t>717149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>722024</t>
+          <t>722023</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396483</t>
+          <t>1396631</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402587</t>
+          <t>1402636</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2958</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57600</t>
+          <t>58015</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110767</t>
+          <t>110578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>3948</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3221</t>
+          <t>3222</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>73509</t>
+          <t>73813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156774</t>
+          <t>156773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3740</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134978</t>
+          <t>134691</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280613</t>
+          <t>281083</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3462</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>617</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4520</t>
+          <t>4572</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701906</t>
+          <t>702348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>745026</t>
+          <t>744680</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1450550</t>
+          <t>1450498</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1455070</t>
+          <t>1454453</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>106672</t>
+          <t>106824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210628</t>
+          <t>210227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3670</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66232</t>
+          <t>65387</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133066</t>
+          <t>132962</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3280</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8482,7 +8482,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4984</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8497,7 +8497,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72782</t>
+          <t>73290</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,7 +8555,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>77904</t>
+          <t>77779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153161</t>
+          <t>153321</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3908</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -9549,7 +9549,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>132779</t>
+          <t>133466</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277051</t>
+          <t>277580</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9784,7 +9784,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9819,7 +9819,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>456</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>160474</t>
+          <t>160394</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>167880</t>
+          <t>167884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330126</t>
+          <t>330519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334569</t>
+          <t>334573</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7162</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>668</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>2566</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,7 +10207,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>697209</t>
+          <t>698002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>703602</t>
+          <t>703765</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>738112</t>
+          <t>737975</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>744170</t>
+          <t>744176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1438717</t>
+          <t>1438793</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1446534</t>
+          <t>1446649</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1009-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1009-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1864,47 +1864,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,107 +2094,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>698</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>698</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3192</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3470</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>7,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3480</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44145</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>42031</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44145</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>41651</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83215</t>
+          <t>83225</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,107 +2780,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>679</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3392</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3111</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3237</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>134976</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>132246</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,5%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,49%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>134976</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>132263</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,5%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>261040</t>
+          <t>261166</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,107 +3123,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3696</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,68%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3477</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1776</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4931</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>5230</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3236,107 +3236,107 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>163363</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>161225</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>156823</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>153609</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>154208</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,32%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,28%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>163363</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>160581</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>320186</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>317031</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>321962</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>491</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>320186</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>316732</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>321515</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>98,38%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,72 +3466,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2072</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1081</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4250</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3695</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,16%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2072</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>677</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5551</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
     </row>
@@ -3579,74 +3579,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>717150</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722021</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>679940</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>676771</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>677326</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,84%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,38%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>717149</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722023</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,23%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2099</t>
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1396631</t>
+          <t>1397099</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1402636</t>
+          <t>1402639</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>619</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2746</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3589</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3147</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -4158,72 +4158,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60142</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>57571</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60142</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58015</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110578</t>
+          <t>110136</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4501,47 +4501,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5074,107 +5074,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>637</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3948</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3518</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,82%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3185</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>637</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3222</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5187,74 +5187,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77124</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73813</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>74243</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,18%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,48%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>225</t>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>156773</t>
+          <t>156810</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5873,47 +5873,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6103,107 +6103,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>4027</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,48%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>665</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3374</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -6216,74 +6216,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138053</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>134691</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>134872</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,52%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>399</t>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>281083</t>
+          <t>280978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6559,47 +6559,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,92 +6789,92 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>3197</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>1303</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>4580</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
         <is>
           <t>619</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>3462</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>617</t>
-        </is>
-      </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>747523</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>744945</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>705625</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>702348</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>702424</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,82%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>747523</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>744680</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2081</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1450498</t>
+          <t>1449877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454453</t>
+          <t>1454451</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7711,107 +7711,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3459</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4003</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -7824,72 +7824,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>109566</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>105956</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>109566</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>106824</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,35%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>210227</t>
+          <t>210643</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7919,7 +7919,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8054,107 +8054,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>734</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4518</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4399</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3774</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8167,72 +8167,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69171</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66215</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,95%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69171</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>65387</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132962</t>
+          <t>132337</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8402,102 +8402,102 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>663</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3812</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,69%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>753</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3671</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4589</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3405</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,96%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1416</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>4862</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1416</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>4824</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8510,74 +8510,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>80521</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>77372</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,31%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76208</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>73290</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>72372</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,02%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,04%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>80521</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>77779</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,81%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>217</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153321</t>
+          <t>153283</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>772</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3846</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,8%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>772</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4983</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>772</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -9539,74 +9539,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>136602</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>133466</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>133528</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,44%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,2%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>414</t>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277580</t>
+          <t>276463</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9769,72 +9769,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3433</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>3782</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3814</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>453</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -9882,74 +9882,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170261</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167416</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>163116</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>160394</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>160362</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>99,35%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>97,7%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170261</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167884</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>513</t>
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>330519</t>
+          <t>330439</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>334573</t>
+          <t>334572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
     </row>
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10117,102 +10117,102 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>6921</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
           <t>2585</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>606</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>6369</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>6577</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2472</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>10690</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>5287</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>10422</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -10225,107 +10225,107 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1061</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>742142</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>737923</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744128</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,64%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1057</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>701786</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>698002</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>703765</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>697794</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>703617</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,63%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>742142</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>737975</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744176</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,89%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>1443928</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>1438525</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>1446743</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,08%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,91%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>1443928</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>1438793</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>1446649</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
